--- a/mlef_pipeline/results/OS_6/SQUAMOUS/training_summary.xlsx
+++ b/mlef_pipeline/results/OS_6/SQUAMOUS/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,59 +548,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD</t>
+          <t>RWD_FMRAD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.661420395421436</v>
+        <v>0.7990916955017302</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05864094948029397</v>
+        <v>0.06670443900800183</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5432099917253507</v>
+        <v>0.7030687569625493</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05977509660771779</v>
+        <v>0.07690811157412256</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7133540605376961</v>
+        <v>0.7227749433106576</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1894436701902948</v>
+        <v>0.1731910317593544</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4878171397732139</v>
+        <v>0.7270975056689343</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2612379233228075</v>
+        <v>0.1057045719589694</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6801470588235292</v>
+        <v>0.5391304347826087</v>
       </c>
       <c r="K2" t="n">
-        <v>0.149596897337297</v>
+        <v>0.2475336790264416</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6033129904097646</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="M2" t="n">
-        <v>0.75</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.7</v>
       </c>
       <c r="O2" t="n">
-        <v>0.618421052631579</v>
+        <v>0.34375</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3160833283604528</v>
+        <v>0.4363822404365377</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7467166979362101</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.25</v>
       </c>
       <c r="S2" t="n">
         <v>0.5</v>
@@ -609,734 +609,231 @@
         <v>11</v>
       </c>
       <c r="U2" t="n">
-        <v>341</v>
+        <v>170</v>
       </c>
       <c r="V2" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="W2" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_DP</t>
+          <t>RWD_FMRAD/rwd-only</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7286184210526315</v>
+        <v>0.5762687427912341</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09381271515477729</v>
+        <v>0.08768744808721352</v>
       </c>
       <c r="D3" t="n">
-        <v>0.567380087523023</v>
+        <v>0.338515082648268</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1159810454395782</v>
+        <v>0.05545583677168944</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6062821092320243</v>
+        <v>0.3998739495798319</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0917047960177825</v>
+        <v>0.4381349324183694</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6483181239388794</v>
+        <v>0.6274509803921569</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2193939072652808</v>
+        <v>0.4624084850802397</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7058823529411764</v>
+        <v>0.6608695652173915</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2824065691973712</v>
+        <v>0.2134351485836726</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5809523809523809</v>
+        <v>0.5642256902761105</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6041666666666665</v>
+        <v>0.53125</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4170588298448651</v>
+        <v>0.4524606073620629</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6135265700483092</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="R3" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T3" t="n">
         <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="V3" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="W3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP/rwd-only</t>
+          <t>RWD_DP_FMRAD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7376644736842105</v>
+        <v>0.9558823529411763</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08949801665850632</v>
+        <v>0.04659970140766873</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3241938943992964</v>
+        <v>0.4749178981937602</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1993462832415605</v>
+        <v>0.1707511562744898</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6230899830220714</v>
+        <v>0.7773809523809525</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4333034254333553</v>
+        <v>0.3130182777041474</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4566532258064516</v>
+        <v>0.4807692307692308</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4736090507723276</v>
+        <v>0.4268686233958858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5705882352941176</v>
+        <v>0.3666666666666665</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2674177974484131</v>
+        <v>0.3644052265135809</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5111111111111111</v>
+        <v>0.4484848484848485</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O4" t="n">
-        <v>0.53125</v>
+        <v>0.5714285714285716</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2569239502449112</v>
+        <v>0.4173916859888483</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5428571428571429</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S4" t="n">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="V4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="W4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD_DP_FMRAD/rwd-only</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7411235955056178</v>
+        <v>0.5821078431372549</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08452306044189695</v>
+        <v>0.155918675555424</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5867905385415906</v>
+        <v>0.2235703873634908</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0658344370260162</v>
+        <v>0.1042084244431412</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5254279639504671</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06674643433703083</v>
+        <v>0.4925123054167483</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7515587529976019</v>
+        <v>0.3793103448275862</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1535210518939472</v>
+        <v>0.48521542343001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7222222222222223</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2203616576597596</v>
+        <v>0.349796479758929</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5571428571428572</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3499935686678668</v>
+        <v>0.2932243558594778</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T5" t="n">
         <v>11</v>
       </c>
       <c r="U5" t="n">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="V5" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RWD_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.6782022471910113</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.09347422160805452</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.3896787265492301</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.1710963602958129</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6182875561898659</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.3935047450935693</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.5007194244604316</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.4519337194157927</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.6464646464646464</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.2032615694231934</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.5441176470588236</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.4642857142857142</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.2935220042913951</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>139</v>
-      </c>
-      <c r="V6" t="n">
-        <v>31</v>
-      </c>
-      <c r="W6" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.6532234105763517</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.08425648701528288</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.5063145526101633</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.08102574293953864</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6400517147523136</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.2801270222917468</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.5313943541488451</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.3534133397117297</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.5391304347826087</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.2386888356995132</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.3541472506989748</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.1739130434782609</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.4407960267350436</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>167</v>
-      </c>
-      <c r="V7" t="n">
-        <v>33</v>
-      </c>
-      <c r="W7" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.6002673796791442</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.08668924243525178</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.4974728773833577</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.05978893698947848</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.5582244601705679</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.3169339890089924</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.5785856857713146</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.3279597105250891</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.7173913043478262</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.1996505296966798</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.593505039193729</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.7826086956521739</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.2818206651206824</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.6210526315789473</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>167</v>
-      </c>
-      <c r="V8" t="n">
-        <v>33</v>
-      </c>
-      <c r="W8" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.9710144927536233</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.03441837376390777</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.9356476856476856</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.09975579960140991</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.8806818181818182</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1957549224653661</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.1333333333333335</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2100134241225386</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.2261904761904762</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.6040569265332552</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>14</v>
-      </c>
-      <c r="U9" t="n">
-        <v>44</v>
-      </c>
-      <c r="V9" t="n">
-        <v>13</v>
-      </c>
-      <c r="W9" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.5559006211180124</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.1924343163480333</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.1730943299125117</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.09318848566177895</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.6136363636363636</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.4869155746733762</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.3863636363636364</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.4869155746733762</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5000000000000002</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>44</v>
-      </c>
-      <c r="V10" t="n">
-        <v>13</v>
-      </c>
-      <c r="W10" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.7473118279569894</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.1335536237687976</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.5908264462809918</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.2237083988484116</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.6289308176100628</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.3013622276908413</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.54644412191582</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.3271563660563248</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.7333333333333336</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.3244290462767792</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.2380952380952381</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.384816120507862</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>55</v>
-      </c>
-      <c r="V11" t="n">
-        <v>13</v>
-      </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.4133064516129031</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.1444794459777607</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.2352600852600853</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.09602795246302552</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.6181818181818182</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.4858323351231777</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.3454545454545455</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.4755162483862553</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.5000000000000002</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
-        <v>0.2307692307692308</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>11</v>
-      </c>
-      <c r="U12" t="n">
-        <v>55</v>
-      </c>
-      <c r="V12" t="n">
-        <v>13</v>
-      </c>
-      <c r="W12" t="n">
         <v>10</v>
       </c>
     </row>

--- a/mlef_pipeline/results/OS_6/SQUAMOUS/training_summary.xlsx
+++ b/mlef_pipeline/results/OS_6/SQUAMOUS/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,292 +548,799 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7990916955017302</v>
+        <v>0.6284562211981567</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06670443900800183</v>
+        <v>0.06086278042516691</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7030687569625493</v>
+        <v>0.5184038351598653</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07690811157412256</v>
+        <v>0.0957137118002182</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7227749433106576</v>
+        <v>0.7136097630314755</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1731910317593544</v>
+        <v>0.1639669110330073</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7270975056689343</v>
+        <v>0.3921864492557698</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1057045719589694</v>
+        <v>0.1778560311368045</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5391304347826087</v>
+        <v>0.7285539215686272</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2475336790264416</v>
+        <v>0.1416148450285548</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5111111111111111</v>
+        <v>0.6971773088517401</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.75</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="O2" t="n">
-        <v>0.34375</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4363822404365377</v>
+        <v>0.232793584318565</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4319775596072931</v>
       </c>
       <c r="R2" t="n">
-        <v>0.25</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="S2" t="n">
         <v>0.5</v>
       </c>
       <c r="T2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U2" t="n">
-        <v>170</v>
+        <v>341</v>
       </c>
       <c r="V2" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="W2" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_FMRAD/rwd-only</t>
+          <t>RWD_DP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5762687427912341</v>
+        <v>0.7214912280701754</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08768744808721352</v>
+        <v>0.09463300560479437</v>
       </c>
       <c r="D3" t="n">
-        <v>0.338515082648268</v>
+        <v>0.5790761433251156</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05545583677168944</v>
+        <v>0.1434981653560014</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3998739495798319</v>
+        <v>0.6533443212135912</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4381349324183694</v>
+        <v>0.1043984795137787</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6274509803921569</v>
+        <v>0.4945882852292021</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4624084850802397</v>
+        <v>0.2453151660547505</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6608695652173915</v>
+        <v>0.7882352941176471</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2134351485836726</v>
+        <v>0.2006875743900054</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5642256902761105</v>
+        <v>0.6178660049627791</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0.53125</v>
+        <v>0.5833333333333335</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4524606073620629</v>
+        <v>0.4337826244390918</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5636363636363637</v>
       </c>
       <c r="R3" t="n">
-        <v>0.875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="S3" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="T3" t="n">
         <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="V3" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="W3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP_FMRAD</t>
+          <t>RWD_DP/rwd-only</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9558823529411763</v>
+        <v>0.7077850877192983</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04659970140766873</v>
+        <v>0.09129463234302859</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4749178981937602</v>
+        <v>0.3241938943992964</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1707511562744898</v>
+        <v>0.1993462832415605</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7773809523809525</v>
+        <v>0.6230899830220714</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3130182777041474</v>
+        <v>0.4333034254333553</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4807692307692308</v>
+        <v>0.4566532258064516</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4268686233958858</v>
+        <v>0.4736090507723276</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3666666666666665</v>
+        <v>0.5705882352941176</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3644052265135809</v>
+        <v>0.2674177974484131</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4484848484848485</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5714285714285716</v>
+        <v>0.53125</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4173916859888483</v>
+        <v>0.2569239502449112</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5833333333333333</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="T4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="U4" t="n">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="V4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="W4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RWD_DP_FMRAD/rwd-only</t>
+          <t>RWD_FMRAD</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5821078431372549</v>
+        <v>0.7990916955017302</v>
       </c>
       <c r="C5" t="n">
-        <v>0.155918675555424</v>
+        <v>0.06670443900800183</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2235703873634908</v>
+        <v>0.7030687569625493</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1042084244431412</v>
+        <v>0.07690811157412256</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.7227749433106576</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4925123054167483</v>
+        <v>0.1731910317593544</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3793103448275862</v>
+        <v>0.7270975056689343</v>
       </c>
       <c r="I5" t="n">
-        <v>0.48521542343001</v>
+        <v>0.1057045719589694</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5391304347826087</v>
       </c>
       <c r="K5" t="n">
-        <v>0.349796479758929</v>
+        <v>0.2475336790264416</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.34375</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2932243558594778</v>
+        <v>0.4363822404365377</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="T5" t="n">
         <v>11</v>
       </c>
       <c r="U5" t="n">
+        <v>170</v>
+      </c>
+      <c r="V5" t="n">
+        <v>33</v>
+      </c>
+      <c r="W5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5762687427912341</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.08768744808721352</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.338515082648268</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05545583677168944</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3998739495798319</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4381349324183694</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6274509803921569</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4624084850802397</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6608695652173915</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2134351485836726</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5642256902761105</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.4524606073620629</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>170</v>
+      </c>
+      <c r="V6" t="n">
+        <v>33</v>
+      </c>
+      <c r="W6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6720142602495545</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.08314401142665362</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6005145287798918</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.07722687275682588</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6568499364906552</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1711878990998822</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5923866552609067</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1537018684462049</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5782608695652176</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2448716849010392</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5147058823529411</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.4135328088344124</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5804195804195804</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T7" t="n">
+        <v>12</v>
+      </c>
+      <c r="U7" t="n">
+        <v>167</v>
+      </c>
+      <c r="V7" t="n">
+        <v>33</v>
+      </c>
+      <c r="W7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6122994652406417</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.08694400735896968</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4946016345585512</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1087640177896336</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2981128651787334</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1393306589799686</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8437696036498431</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.08132420041915378</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6260869565217391</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2234402413585973</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3043478260869565</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.3078286047871139</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>167</v>
+      </c>
+      <c r="V8" t="n">
+        <v>33</v>
+      </c>
+      <c r="W8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9558823529411763</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.04659970140766873</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4749178981937602</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1707511562744898</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7773809523809525</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3130182777041474</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4807692307692308</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4268686233958858</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3666666666666665</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.3644052265135809</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4484848484848485</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5714285714285716</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4173916859888483</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T9" t="n">
+        <v>11</v>
+      </c>
+      <c r="U9" t="n">
         <v>58</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V9" t="n">
         <v>13</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.5821078431372549</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.155918675555424</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2235703873634908</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1042084244431412</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5862068965517241</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4925123054167483</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3793103448275862</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.48521542343001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.349796479758929</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.2932243558594778</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>58</v>
+      </c>
+      <c r="V10" t="n">
+        <v>13</v>
+      </c>
+      <c r="W10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7473118279569894</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1335536237687976</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5908264462809918</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2237083988484116</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6289308176100628</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3013622276908413</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.54644412191582</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3271563660563248</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7333333333333336</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.3244290462767792</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.384816120507862</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>55</v>
+      </c>
+      <c r="V11" t="n">
+        <v>13</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.3864247311827956</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1456923176048509</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2716237216237217</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1647812658821962</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6415094339622641</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4795571708354277</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3584905660377358</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4795571708354277</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5000000000000002</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>55</v>
+      </c>
+      <c r="V12" t="n">
+        <v>13</v>
+      </c>
+      <c r="W12" t="n">
         <v>10</v>
       </c>
     </row>
